--- a/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
+++ b/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\dashboards\world_cup_dashboard\src\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D6A4B0-97DB-4AFB-9EA6-26FCFFA4E910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4562C1A-1E1A-4A46-9F2B-EF3092D7301C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="277">
   <si>
     <t>ID</t>
   </si>
@@ -840,6 +840,30 @@
   </si>
   <si>
     <t>Saudi Arabia;</t>
+  </si>
+  <si>
+    <t>anonymous</t>
+  </si>
+  <si>
+    <t>Rosie Davies</t>
+  </si>
+  <si>
+    <t>France;England;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciara </t>
+  </si>
+  <si>
+    <t>Qatar;New Zealand ;</t>
+  </si>
+  <si>
+    <t>Austria;Canada;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damon </t>
+  </si>
+  <si>
+    <t>Alex</t>
   </si>
 </sst>
 </file>
@@ -878,9 +902,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,8 +970,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:O80" totalsRowShown="0">
-  <autoFilter ref="A1:O80" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:O85" totalsRowShown="0">
+  <autoFilter ref="A1:O85" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="13"/>
@@ -1265,7 +1290,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="15" width="20" bestFit="1" customWidth="1"/>
@@ -3564,6 +3589,175 @@
         <v>19</v>
       </c>
     </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46177.614004629599</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46177.615717592598</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46177.614537037</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46177.619768518503</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F82" s="1"/>
+      <c r="G82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46177.634513888901</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46177.638206018499</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="1"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46178.286504629599</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46178.289583333302</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F84" s="1"/>
+      <c r="G84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46185.351053240702</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46185.352928240703</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F85" s="1"/>
+      <c r="G85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O85" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
+++ b/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4562C1A-1E1A-4A46-9F2B-EF3092D7301C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625A035D-03D2-4DB4-B7E3-698E77A44F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="199">
   <si>
     <t>ID</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Grant.Barrott@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Grant Barrott</t>
-  </si>
-  <si>
     <t>France;</t>
   </si>
   <si>
@@ -116,9 +113,6 @@
     <t>Suzanne.Stew@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Suzanne Stew</t>
-  </si>
-  <si>
     <t>Germany;</t>
   </si>
   <si>
@@ -131,18 +125,12 @@
     <t>Henry.Fry@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Henry Fry</t>
-  </si>
-  <si>
     <t>Iran;</t>
   </si>
   <si>
     <t>Mathieson.Carlyle@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Mathieson Carlyle</t>
-  </si>
-  <si>
     <t>Norway;</t>
   </si>
   <si>
@@ -155,9 +143,6 @@
     <t>Elliott.Bonnett@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Elliott Bonnett</t>
-  </si>
-  <si>
     <t>Mexico;</t>
   </si>
   <si>
@@ -170,9 +155,6 @@
     <t>Elliot.Davis@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Elliot Davis</t>
-  </si>
-  <si>
     <t>Belgium;</t>
   </si>
   <si>
@@ -191,9 +173,6 @@
     <t>Ann.Upchurch@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Ann Upchurch</t>
-  </si>
-  <si>
     <t>Brazil;</t>
   </si>
   <si>
@@ -206,9 +185,6 @@
     <t>Caleb.Matthews@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Caleb Matthews</t>
-  </si>
-  <si>
     <t>Ecuador;</t>
   </si>
   <si>
@@ -221,9 +197,6 @@
     <t>Ollie.Martin@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Ollie Martin</t>
-  </si>
-  <si>
     <t>Senegal;Ecuador;Croatia;</t>
   </si>
   <si>
@@ -233,18 +206,12 @@
     <t>Christo.Matheson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Christo Matheson</t>
-  </si>
-  <si>
     <t>Iraq;</t>
   </si>
   <si>
     <t>Daniel.Taylor@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Daniel Taylor</t>
-  </si>
-  <si>
     <t>Mexico;Japan;</t>
   </si>
   <si>
@@ -254,9 +221,6 @@
     <t>Frankie.Toland@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Frankie Toland</t>
-  </si>
-  <si>
     <t>England;Spain;France;</t>
   </si>
   <si>
@@ -287,9 +251,6 @@
     <t>Ryan.Wilkinson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Ryan Wilkinson</t>
-  </si>
-  <si>
     <t>DR Congo;Uzbekistan;Iraq;Cape Verde;Panama;</t>
   </si>
   <si>
@@ -299,18 +260,12 @@
     <t>Max.Taylor-Smith@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Max Taylor-Smith</t>
-  </si>
-  <si>
     <t>Australia;South Africa;</t>
   </si>
   <si>
     <t>Claudia.Wilkinson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Claudia Wilkinson</t>
-  </si>
-  <si>
     <t>Portugal;</t>
   </si>
   <si>
@@ -320,9 +275,6 @@
     <t>Kim.McCormick@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Kim McCormick</t>
-  </si>
-  <si>
     <t>Croatia;Sweeden;</t>
   </si>
   <si>
@@ -332,36 +284,24 @@
     <t>Jackson.Middleton@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Jackson Middleton</t>
-  </si>
-  <si>
     <t>Cape Verde;</t>
   </si>
   <si>
     <t>Abby.Robinson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Abby Robinson</t>
-  </si>
-  <si>
     <t>Croatia;Switzerland;</t>
   </si>
   <si>
     <t>Rose.Watson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Rose Watson</t>
-  </si>
-  <si>
     <t>Argentina;Portugal;</t>
   </si>
   <si>
     <t>Karen.Rand@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Karen Rand</t>
-  </si>
-  <si>
     <t>England;</t>
   </si>
   <si>
@@ -374,9 +314,6 @@
     <t>aidan.winder-speed@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Aidan Winder-Speed</t>
-  </si>
-  <si>
     <t>Netherlands;Norway;</t>
   </si>
   <si>
@@ -386,9 +323,6 @@
     <t>Matthew.Steiner@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Matthew Steiner</t>
-  </si>
-  <si>
     <t>Morocco;</t>
   </si>
   <si>
@@ -401,198 +335,117 @@
     <t>Daniel.Pringle@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Daniel Pringle</t>
-  </si>
-  <si>
     <t>Paul.Cho@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Paul Cho</t>
-  </si>
-  <si>
     <t>Switzerland;</t>
   </si>
   <si>
     <t>david.chrystall@comcom.govt.nz</t>
   </si>
   <si>
-    <t>David Chrystall</t>
-  </si>
-  <si>
     <t>Switzerland;Sweeden;</t>
   </si>
   <si>
     <t>Jordan.Hamilton@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Jordan Hamilton</t>
-  </si>
-  <si>
     <t>Sam.Bull@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Sam Bull</t>
-  </si>
-  <si>
     <t>Ecuador;Senegal;Croatia;</t>
   </si>
   <si>
     <t>Sartaj.Bedi@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Sartaj Bedi</t>
-  </si>
-  <si>
     <t>Martha.Mallon@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Martha Mallon</t>
-  </si>
-  <si>
     <t>England;Spain;</t>
   </si>
   <si>
     <t>Laura.Pringle@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Laura Pringle</t>
-  </si>
-  <si>
     <t>New Zealand ;Curacao;</t>
   </si>
   <si>
     <t>Bridgette.Chisnall@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Bridgette Chisnall</t>
-  </si>
-  <si>
     <t>Luke.Archer@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Luke Archer</t>
-  </si>
-  <si>
     <t>Stephanie.McGregor@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Stephanie McGregor</t>
-  </si>
-  <si>
     <t>Matthew.Bailey@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Matthew Bailey</t>
-  </si>
-  <si>
     <t>Switzerland;Croatia;</t>
   </si>
   <si>
     <t>Matthew.Moloney@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Matthew Moloney</t>
-  </si>
-  <si>
     <t>Sven.Mol@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Sven Mol</t>
-  </si>
-  <si>
     <t>Tendai.Makova@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Tendai Makova</t>
-  </si>
-  <si>
     <t>Bosnia;Paraguay;</t>
   </si>
   <si>
     <t>Charlotte.Meyer@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Charlotte Meyer</t>
-  </si>
-  <si>
     <t>South Africa;</t>
   </si>
   <si>
     <t>Charlotte.Brown@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Charlotte Brown</t>
-  </si>
-  <si>
     <t>Kylee.Garlick@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Kylee Garlick</t>
-  </si>
-  <si>
     <t>Rhyno.Heydenrych@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Rhyno Heydenrych</t>
-  </si>
-  <si>
     <t>Marc.Lorentzen@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Marc Lorentzen</t>
-  </si>
-  <si>
     <t>Austria;Egypt;</t>
   </si>
   <si>
     <t>Kirsten.Dinnan@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Kirsten Dinnan</t>
-  </si>
-  <si>
     <t>Sylvie.Gray@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Sylvie Gray</t>
-  </si>
-  <si>
     <t>Michael.Chatwin2@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Michael Chatwin</t>
-  </si>
-  <si>
     <t>Abby.Galland@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Abby Galland</t>
-  </si>
-  <si>
     <t>USA;</t>
   </si>
   <si>
     <t>nick.wilkins@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Nick Wilkins</t>
-  </si>
-  <si>
     <t>Egypt;</t>
   </si>
   <si>
     <t>Claire.Phipps@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Claire Phipps</t>
-  </si>
-  <si>
     <t>Sarah.Bates2@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Sarah Bates</t>
-  </si>
-  <si>
     <t>Croatia;Turkey;</t>
   </si>
   <si>
@@ -602,24 +455,15 @@
     <t>Daniel.Wypych@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Daniel Wypych</t>
-  </si>
-  <si>
     <t>South Korea;Iran;</t>
   </si>
   <si>
     <t>Matthew.Lewer@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Matthew Lewer</t>
-  </si>
-  <si>
     <t>Jayden.Ravji@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Jayden Ravji</t>
-  </si>
-  <si>
     <t>Australia;Iran;South Korea;</t>
   </si>
   <si>
@@ -632,9 +476,6 @@
     <t>Nicci.Coffey@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Nicci Coffey</t>
-  </si>
-  <si>
     <t>Colombia;</t>
   </si>
   <si>
@@ -647,60 +488,36 @@
     <t>Irene.Kilford@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Irene Kilford</t>
-  </si>
-  <si>
     <t>Spain;France;</t>
   </si>
   <si>
     <t>Rachael.Peonides@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Rachael Peonides</t>
-  </si>
-  <si>
     <t>Natalie.Reid@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Natalie Reid</t>
-  </si>
-  <si>
     <t>Zac.Clark@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Zac Clark</t>
-  </si>
-  <si>
     <t>Jenna.MachadodaCruz@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Jenna Machado da Cruz</t>
-  </si>
-  <si>
     <t>Ivory Coast;</t>
   </si>
   <si>
     <t>Grant.McIntosh@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Grant McIntosh</t>
-  </si>
-  <si>
     <t>Harry.Trainor@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Harry Trainor</t>
-  </si>
-  <si>
     <t>France;Spain;</t>
   </si>
   <si>
     <t>Simon.Wakefield@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Simon Wakefield</t>
-  </si>
-  <si>
     <t>Mexico;USA;</t>
   </si>
   <si>
@@ -710,42 +527,27 @@
     <t>Olaf.Stypa@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Olaf Stypa</t>
-  </si>
-  <si>
     <t>Czech Republic;</t>
   </si>
   <si>
     <t>Louise.Stephenson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Louise Stephenson</t>
-  </si>
-  <si>
     <t>Scotland;Canada;</t>
   </si>
   <si>
     <t>Paddy.Plunket@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Paddy Plunket</t>
-  </si>
-  <si>
     <t>Tunisia;Saudi Arabia;South Korea;Iran;South Africa;Australia;</t>
   </si>
   <si>
     <t>Thulani.Mandiriza@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Thulani Mandiriza</t>
-  </si>
-  <si>
     <t>Matt.Croxford@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Matt Croxford</t>
-  </si>
-  <si>
     <t>Ecuador;Croatia;</t>
   </si>
   <si>
@@ -755,24 +557,15 @@
     <t>Finnan.Ralph@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Finnan Ralph</t>
-  </si>
-  <si>
     <t>Turkey;Switzerland;</t>
   </si>
   <si>
     <t>Anna.Jefferson@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Anna Jefferson</t>
-  </si>
-  <si>
     <t>Robert.Chiu@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Robert Chiu</t>
-  </si>
-  <si>
     <t>Japan;USA;</t>
   </si>
   <si>
@@ -782,63 +575,36 @@
     <t>Cameron.Megaw@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Cameron Megaw</t>
-  </si>
-  <si>
     <t>Ania.Mroczka@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Ania Mroczka</t>
-  </si>
-  <si>
     <t>Ricky.Ho@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Ricky Ho</t>
-  </si>
-  <si>
     <t>Ecuador;Switzerland;</t>
   </si>
   <si>
     <t>James.Evans@comcom.govt.nz</t>
   </si>
   <si>
-    <t>James Evans</t>
-  </si>
-  <si>
     <t>Hamish.Buller@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Hamish Buller</t>
-  </si>
-  <si>
     <t>Conor.Farrell@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Conor Farrell</t>
-  </si>
-  <si>
     <t>Maree.VanderZouwe@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Maree van der Zouwe</t>
-  </si>
-  <si>
     <t>Philia.Yeo@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Philia Yeo</t>
-  </si>
-  <si>
     <t>South Korea;Australia;Iran;</t>
   </si>
   <si>
     <t>Elliot.Grant2@comcom.govt.nz</t>
   </si>
   <si>
-    <t>Elliot Grant</t>
-  </si>
-  <si>
     <t>Saudi Arabia;</t>
   </si>
   <si>
@@ -851,19 +617,19 @@
     <t>France;England;</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciara </t>
-  </si>
-  <si>
     <t>Qatar;New Zealand ;</t>
   </si>
   <si>
     <t>Austria;Canada;</t>
   </si>
   <si>
-    <t xml:space="preserve">Damon </t>
-  </si>
-  <si>
-    <t>Alex</t>
+    <t>Ciara Moriarty</t>
+  </si>
+  <si>
+    <t>Damon Muollo</t>
+  </si>
+  <si>
+    <t>Alex Davies</t>
   </si>
 </sst>
 </file>
@@ -902,10 +668,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1356,9 +1121,6 @@
       <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
       <c r="F2" s="1">
         <v>46176.646435185197</v>
       </c>
@@ -1391,17 +1153,14 @@
       <c r="D3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
       <c r="F3" s="1">
         <v>46176.636064814797</v>
       </c>
       <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
       </c>
       <c r="M3" t="s">
         <v>19</v>
@@ -1418,20 +1177,17 @@
         <v>46176.643888888902</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4" s="1"/>
       <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
         <v>28</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -1445,20 +1201,17 @@
         <v>46176.644236111097</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="I5" t="s">
-        <v>25</v>
-      </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -1472,23 +1225,20 @@
         <v>46176.644282407397</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
         <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="N6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -1502,23 +1252,20 @@
         <v>46176.645023148099</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
         <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="N7" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1532,26 +1279,23 @@
         <v>46176.645243055602</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F8" s="1"/>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="O8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1565,23 +1309,20 @@
         <v>46176.645370370403</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1"/>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
@@ -1595,23 +1336,20 @@
         <v>46176.645532407398</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
         <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="M10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="N10" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -1628,20 +1366,17 @@
         <v>46176.645937499998</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1"/>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
@@ -1655,23 +1390,20 @@
         <v>46176.645949074104</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F12" s="1"/>
       <c r="H12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J12" t="s">
         <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
@@ -1685,20 +1417,17 @@
         <v>46176.646585648101</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F13" s="1"/>
       <c r="J13" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="K13" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -1712,38 +1441,35 @@
         <v>46176.646932870397</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K14" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="M14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="O14" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
@@ -1757,20 +1483,17 @@
         <v>46176.646944444401</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="F15" s="1"/>
       <c r="M15" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="N15" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O15" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -1784,17 +1507,14 @@
         <v>46176.6477662037</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F16" s="1"/>
       <c r="M16" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="O16" t="s">
         <v>21</v>
@@ -1811,20 +1531,17 @@
         <v>46176.647847222201</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1"/>
       <c r="H17" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -1838,25 +1555,22 @@
         <v>46176.648587962998</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F18" s="1">
         <v>46184.3461805556</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K18" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="N18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
@@ -1873,23 +1587,20 @@
         <v>46176.6488425926</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F19" s="1"/>
       <c r="H19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
         <v>18</v>
       </c>
       <c r="K19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N19" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -1903,17 +1614,14 @@
         <v>46176.6495601852</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K20" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="M20" t="s">
         <v>19</v>
@@ -1930,17 +1638,14 @@
         <v>46176.650023148097</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="F21" s="1"/>
       <c r="H21" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="M21" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -1954,20 +1659,17 @@
         <v>46176.650266203702</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="O22" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -1981,23 +1683,20 @@
         <v>46176.650902777801</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="F23" s="1"/>
       <c r="I23" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="M23" t="s">
         <v>19</v>
       </c>
       <c r="N23" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="O23" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -2011,23 +1710,20 @@
         <v>46176.650902777801</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
-      </c>
-      <c r="E24" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="F24" s="1"/>
       <c r="J24" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K24" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L24" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="M24" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -2041,23 +1737,20 @@
         <v>46176.651400463001</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="F25" s="1"/>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J25" t="s">
         <v>18</v>
       </c>
       <c r="L25" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M25" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -2071,10 +1764,7 @@
         <v>46176.653113425898</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" t="s">
@@ -2084,7 +1774,7 @@
         <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -2098,17 +1788,14 @@
         <v>46176.654432870397</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
-      </c>
-      <c r="E27" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K27" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="M27" t="s">
         <v>19</v>
@@ -2125,20 +1812,17 @@
         <v>46176.655104166697</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F28" s="1"/>
       <c r="H28" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
         <v>18</v>
       </c>
       <c r="K28" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="O28" t="s">
         <v>21</v>
@@ -2155,17 +1839,14 @@
         <v>46176.662557870397</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="F29" s="1"/>
       <c r="I29" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K29" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -2179,26 +1860,23 @@
         <v>46176.665879629603</v>
       </c>
       <c r="D30" t="s">
-        <v>134</v>
-      </c>
-      <c r="E30" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" t="s">
         <v>17</v>
       </c>
       <c r="K30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M30" t="s">
         <v>19</v>
       </c>
       <c r="O30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -2212,14 +1890,11 @@
         <v>46176.668009259301</v>
       </c>
       <c r="D31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E31" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -2233,23 +1908,20 @@
         <v>46176.668472222198</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
-      </c>
-      <c r="E32" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F32" s="1"/>
       <c r="H32" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K32" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O32" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
@@ -2263,20 +1935,17 @@
         <v>46176.6691319444</v>
       </c>
       <c r="D33" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" t="s">
         <v>17</v>
       </c>
       <c r="J33" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K33" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
@@ -2290,23 +1959,20 @@
         <v>46176.681388888901</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="F34" s="1"/>
       <c r="H34" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J34" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K34" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="O34" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
@@ -2320,17 +1986,14 @@
         <v>46176.684641203698</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
-      </c>
-      <c r="E35" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H35" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O35" t="s">
         <v>21</v>
@@ -2347,20 +2010,17 @@
         <v>46176.6847569444</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K36" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="M36" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
@@ -2374,17 +2034,14 @@
         <v>46176.7093171296</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" t="s">
         <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M37" t="s">
         <v>19</v>
@@ -2401,20 +2058,17 @@
         <v>46176.7570023148</v>
       </c>
       <c r="D38" t="s">
-        <v>153</v>
-      </c>
-      <c r="E38" t="s">
-        <v>154</v>
+        <v>118</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" t="s">
         <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M38" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -2428,20 +2082,17 @@
         <v>46177.010694444398</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
-      </c>
-      <c r="E39" t="s">
-        <v>156</v>
+        <v>119</v>
       </c>
       <c r="F39" s="1"/>
       <c r="I39" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K39" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L39" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="M39" t="s">
         <v>19</v>
@@ -2458,20 +2109,17 @@
         <v>46177.333530092597</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
-      </c>
-      <c r="E40" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M40" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
@@ -2485,14 +2133,11 @@
         <v>46177.378946759301</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
-      </c>
-      <c r="E41" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
@@ -2506,26 +2151,23 @@
         <v>46177.381782407399</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
-      </c>
-      <c r="E42" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K42" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L42" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M42" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="O42" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
@@ -2539,23 +2181,20 @@
         <v>46177.381990740701</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
-      </c>
-      <c r="E43" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="F43" s="1"/>
       <c r="H43" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L43" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
@@ -2569,20 +2208,17 @@
         <v>46177.384467592601</v>
       </c>
       <c r="D44" t="s">
-        <v>167</v>
-      </c>
-      <c r="E44" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="F44" s="1"/>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K44" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L44" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="M44" t="s">
         <v>19</v>
@@ -2599,17 +2235,14 @@
         <v>46177.395682870403</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" t="s">
         <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="O45" t="s">
         <v>21</v>
@@ -2626,20 +2259,17 @@
         <v>46177.401261574101</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
-      </c>
-      <c r="E46" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" t="s">
         <v>17</v>
       </c>
       <c r="H46" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O46" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
@@ -2653,20 +2283,17 @@
         <v>46177.406527777799</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
-      </c>
-      <c r="E47" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K47" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
@@ -2680,20 +2307,17 @@
         <v>46177.426354166702</v>
       </c>
       <c r="D48" t="s">
-        <v>176</v>
-      </c>
-      <c r="E48" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" t="s">
         <v>17</v>
       </c>
       <c r="J48" t="s">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="K48" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
@@ -2707,23 +2331,20 @@
         <v>46177.480682870402</v>
       </c>
       <c r="D49" t="s">
-        <v>179</v>
-      </c>
-      <c r="E49" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="F49" s="1"/>
       <c r="H49" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="K49" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L49" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="M49" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
@@ -2737,17 +2358,14 @@
         <v>46177.611122685201</v>
       </c>
       <c r="D50" t="s">
-        <v>182</v>
-      </c>
-      <c r="E50" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" t="s">
         <v>17</v>
       </c>
       <c r="H50" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N50" t="s">
         <v>20</v>
@@ -2764,26 +2382,23 @@
         <v>46177.677743055603</v>
       </c>
       <c r="D51" t="s">
-        <v>184</v>
-      </c>
-      <c r="E51" t="s">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="F51" s="1"/>
       <c r="I51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K51" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="N51" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="O51" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
@@ -2797,23 +2412,20 @@
         <v>46177.7012384259</v>
       </c>
       <c r="D52" t="s">
-        <v>188</v>
-      </c>
-      <c r="E52" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="F52" s="1"/>
       <c r="J52" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K52" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L52" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="M52" t="s">
-        <v>190</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
@@ -2827,23 +2439,20 @@
         <v>46177.711539351803</v>
       </c>
       <c r="D53" t="s">
-        <v>191</v>
-      </c>
-      <c r="E53" t="s">
-        <v>192</v>
+        <v>141</v>
       </c>
       <c r="F53" s="1"/>
       <c r="H53" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J53" t="s">
         <v>18</v>
       </c>
       <c r="L53" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M53" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
@@ -2857,23 +2466,20 @@
         <v>46177.711678240703</v>
       </c>
       <c r="D54" t="s">
-        <v>193</v>
-      </c>
-      <c r="E54" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="N54" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="O54" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
@@ -2887,26 +2493,23 @@
         <v>46177.879837963003</v>
       </c>
       <c r="D55" t="s">
-        <v>198</v>
-      </c>
-      <c r="E55" t="s">
-        <v>199</v>
+        <v>146</v>
       </c>
       <c r="F55" s="1"/>
       <c r="I55" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="K55" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L55" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="N55" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="O55" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
@@ -2920,14 +2523,11 @@
         <v>46178.247546296298</v>
       </c>
       <c r="D56" t="s">
-        <v>203</v>
-      </c>
-      <c r="E56" t="s">
-        <v>204</v>
+        <v>150</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
@@ -2941,17 +2541,14 @@
         <v>46178.3500347222</v>
       </c>
       <c r="D57" t="s">
-        <v>206</v>
-      </c>
-      <c r="E57" t="s">
-        <v>207</v>
+        <v>152</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M57" t="s">
         <v>19</v>
@@ -2968,20 +2565,17 @@
         <v>46178.3539467593</v>
       </c>
       <c r="D58" t="s">
-        <v>208</v>
-      </c>
-      <c r="E58" t="s">
-        <v>209</v>
+        <v>153</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H58" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="N58" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
@@ -2995,22 +2589,19 @@
         <v>46178.3766666667</v>
       </c>
       <c r="D59" t="s">
-        <v>210</v>
-      </c>
-      <c r="E59" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="F59" s="1">
         <v>46178.3821412037</v>
       </c>
       <c r="G59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H59" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O59" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
@@ -3024,20 +2615,17 @@
         <v>46178.426701388897</v>
       </c>
       <c r="D60" t="s">
-        <v>212</v>
-      </c>
-      <c r="E60" t="s">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J60" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="L60" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="O60" t="s">
         <v>21</v>
@@ -3054,20 +2642,17 @@
         <v>46178.4547916667</v>
       </c>
       <c r="D61" t="s">
-        <v>215</v>
-      </c>
-      <c r="E61" t="s">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="F61" s="1"/>
       <c r="H61" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J61" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K61" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="O61" t="s">
         <v>21</v>
@@ -3084,14 +2669,11 @@
         <v>46178.459837962997</v>
       </c>
       <c r="D62" t="s">
-        <v>217</v>
-      </c>
-      <c r="E62" t="s">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" t="s">
-        <v>219</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
@@ -3105,17 +2687,14 @@
         <v>46178.465358796297</v>
       </c>
       <c r="D63" t="s">
-        <v>220</v>
-      </c>
-      <c r="E63" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="F63" s="1"/>
       <c r="J63" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="K63" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
@@ -3129,20 +2708,17 @@
         <v>46178.553252314799</v>
       </c>
       <c r="D64" t="s">
-        <v>224</v>
-      </c>
-      <c r="E64" t="s">
-        <v>225</v>
+        <v>163</v>
       </c>
       <c r="F64" s="1"/>
       <c r="H64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L64" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
@@ -3156,23 +2732,20 @@
         <v>46181.392592592601</v>
       </c>
       <c r="D65" t="s">
-        <v>227</v>
-      </c>
-      <c r="E65" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="F65" s="1"/>
       <c r="H65" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K65" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L65" t="s">
-        <v>229</v>
+        <v>166</v>
       </c>
       <c r="O65" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
@@ -3186,20 +2759,17 @@
         <v>46181.393981481502</v>
       </c>
       <c r="D66" t="s">
-        <v>230</v>
-      </c>
-      <c r="E66" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="F66" s="1"/>
       <c r="M66" t="s">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="N66" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="O66" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
@@ -3213,14 +2783,11 @@
         <v>46181.398506944402</v>
       </c>
       <c r="D67" t="s">
-        <v>233</v>
-      </c>
-      <c r="E67" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
@@ -3234,20 +2801,17 @@
         <v>46181.433229166701</v>
       </c>
       <c r="D68" t="s">
-        <v>235</v>
-      </c>
-      <c r="E68" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="F68" s="1"/>
       <c r="H68" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K68" t="s">
-        <v>237</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
@@ -3261,20 +2825,17 @@
         <v>46181.637094907397</v>
       </c>
       <c r="D69" t="s">
-        <v>239</v>
-      </c>
-      <c r="E69" t="s">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="F69" s="1"/>
       <c r="H69" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K69" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
       <c r="L69" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
@@ -3288,20 +2849,17 @@
         <v>46182.609456018501</v>
       </c>
       <c r="D70" t="s">
-        <v>242</v>
-      </c>
-      <c r="E70" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="F70" s="1"/>
       <c r="H70" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J70" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="L70" t="s">
-        <v>214</v>
+        <v>156</v>
       </c>
       <c r="M70" t="s">
         <v>19</v>
@@ -3318,20 +2876,17 @@
         <v>46182.626099537003</v>
       </c>
       <c r="D71" t="s">
-        <v>244</v>
-      </c>
-      <c r="E71" t="s">
-        <v>245</v>
+        <v>176</v>
       </c>
       <c r="F71" s="1"/>
       <c r="J71" t="s">
-        <v>246</v>
+        <v>177</v>
       </c>
       <c r="K71" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M71" t="s">
-        <v>247</v>
+        <v>178</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
@@ -3345,20 +2900,17 @@
         <v>46182.649814814802</v>
       </c>
       <c r="D72" t="s">
-        <v>248</v>
-      </c>
-      <c r="E72" t="s">
-        <v>249</v>
+        <v>179</v>
       </c>
       <c r="F72" s="1"/>
       <c r="H72" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K72" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="L72" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
@@ -3372,20 +2924,17 @@
         <v>46183.398240740702</v>
       </c>
       <c r="D73" t="s">
-        <v>250</v>
-      </c>
-      <c r="E73" t="s">
-        <v>251</v>
+        <v>180</v>
       </c>
       <c r="F73" s="1"/>
       <c r="I73" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J73" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K73" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="M73" t="s">
         <v>19</v>
@@ -3402,17 +2951,14 @@
         <v>46183.4283796296</v>
       </c>
       <c r="D74" t="s">
-        <v>252</v>
-      </c>
-      <c r="E74" t="s">
-        <v>253</v>
+        <v>181</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" t="s">
         <v>17</v>
       </c>
       <c r="K74" t="s">
-        <v>254</v>
+        <v>182</v>
       </c>
       <c r="M74" t="s">
         <v>19</v>
@@ -3429,10 +2975,7 @@
         <v>46183.616145833301</v>
       </c>
       <c r="D75" t="s">
-        <v>255</v>
-      </c>
-      <c r="E75" t="s">
-        <v>256</v>
+        <v>183</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" t="s">
@@ -3442,7 +2985,7 @@
         <v>18</v>
       </c>
       <c r="K75" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
@@ -3456,20 +2999,17 @@
         <v>46183.632256944402</v>
       </c>
       <c r="D76" t="s">
-        <v>257</v>
-      </c>
-      <c r="E76" t="s">
-        <v>258</v>
+        <v>184</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" t="s">
         <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="L76" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="M76" t="s">
         <v>19</v>
@@ -3489,20 +3029,17 @@
         <v>46183.705995370401</v>
       </c>
       <c r="D77" t="s">
-        <v>259</v>
-      </c>
-      <c r="E77" t="s">
-        <v>260</v>
+        <v>185</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" t="s">
         <v>17</v>
       </c>
       <c r="J77" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="K77" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
@@ -3516,20 +3053,17 @@
         <v>46184.321180555598</v>
       </c>
       <c r="D78" t="s">
-        <v>261</v>
-      </c>
-      <c r="E78" t="s">
-        <v>262</v>
+        <v>186</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" t="s">
         <v>24</v>
       </c>
-      <c r="I78" t="s">
-        <v>25</v>
-      </c>
       <c r="M78" t="s">
-        <v>268</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
@@ -3543,23 +3077,20 @@
         <v>46184.375601851803</v>
       </c>
       <c r="D79" t="s">
-        <v>263</v>
-      </c>
-      <c r="E79" t="s">
-        <v>264</v>
+        <v>187</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" t="s">
         <v>17</v>
       </c>
       <c r="L79" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M79" t="s">
-        <v>265</v>
+        <v>188</v>
       </c>
       <c r="O79" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
@@ -3573,24 +3104,21 @@
         <v>46184.403912037</v>
       </c>
       <c r="D80" t="s">
-        <v>266</v>
-      </c>
-      <c r="E80" t="s">
-        <v>267</v>
+        <v>189</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" t="s">
         <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="M80" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A81" s="2">
+      <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" s="1">
@@ -3599,27 +3127,19 @@
       <c r="C81" s="1">
         <v>46177.615717592598</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>270</v>
+      <c r="D81" t="s">
+        <v>191</v>
+      </c>
+      <c r="E81" t="s">
+        <v>192</v>
       </c>
       <c r="F81" s="1"/>
-      <c r="G81" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
-      <c r="K81" s="2"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="G81" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A82" s="2">
+      <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" s="1">
@@ -3628,31 +3148,25 @@
       <c r="C82" s="1">
         <v>46177.619768518503</v>
       </c>
-      <c r="D82" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>272</v>
+      <c r="D82" t="s">
+        <v>191</v>
+      </c>
+      <c r="E82" t="s">
+        <v>196</v>
       </c>
       <c r="F82" s="1"/>
-      <c r="G82" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2" t="s">
-        <v>273</v>
+      <c r="G82" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" t="s">
+        <v>26</v>
+      </c>
+      <c r="O82" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A83" s="2">
+      <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="1">
@@ -3661,37 +3175,34 @@
       <c r="C83" s="1">
         <v>46177.638206018499</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="D83" t="s">
+        <v>191</v>
+      </c>
+      <c r="E83" t="s">
         <v>16</v>
       </c>
       <c r="F83" s="1"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="M83" s="2" t="s">
+      <c r="J83" t="s">
+        <v>96</v>
+      </c>
+      <c r="K83" t="s">
+        <v>101</v>
+      </c>
+      <c r="L83" t="s">
+        <v>195</v>
+      </c>
+      <c r="M83" t="s">
         <v>19</v>
       </c>
-      <c r="N83" s="2" t="s">
+      <c r="N83" t="s">
         <v>20</v>
       </c>
-      <c r="O83" s="2" t="s">
-        <v>115</v>
+      <c r="O83" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A84" s="2">
+      <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" s="1">
@@ -3700,33 +3211,28 @@
       <c r="C84" s="1">
         <v>46178.289583333302</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>275</v>
+      <c r="D84" t="s">
+        <v>191</v>
+      </c>
+      <c r="E84" t="s">
+        <v>197</v>
       </c>
       <c r="F84" s="1"/>
-      <c r="G84" s="2" t="s">
+      <c r="G84" t="s">
         <v>17</v>
       </c>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2" t="s">
+      <c r="J84" t="s">
         <v>18</v>
       </c>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2" t="s">
-        <v>141</v>
+      <c r="L84" t="s">
+        <v>156</v>
+      </c>
+      <c r="O84" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A85" s="2">
+      <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" s="1">
@@ -3735,28 +3241,22 @@
       <c r="C85" s="1">
         <v>46185.352928240703</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>276</v>
+      <c r="D85" t="s">
+        <v>191</v>
+      </c>
+      <c r="E85" t="s">
+        <v>198</v>
       </c>
       <c r="F85" s="1"/>
-      <c r="G85" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I85" s="2"/>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="O85" s="2"/>
+      <c r="G85" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" t="s">
+        <v>46</v>
+      </c>
+      <c r="N85" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
+++ b/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{625A035D-03D2-4DB4-B7E3-698E77A44F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF119A7-3B45-41E2-B192-21AB442934B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="119">
   <si>
     <t>ID</t>
   </si>
@@ -80,9 +80,6 @@
 </t>
   </si>
   <si>
-    <t>Sam.Wright@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Sam Wright</t>
   </si>
   <si>
@@ -101,18 +98,12 @@
     <t>New Zealand ;Qatar;</t>
   </si>
   <si>
-    <t>Grant.Barrott@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>France;</t>
   </si>
   <si>
     <t>Netherlands;</t>
   </si>
   <si>
-    <t>Suzanne.Stew@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Germany;</t>
   </si>
   <si>
@@ -122,15 +113,9 @@
     <t>Scotland;</t>
   </si>
   <si>
-    <t>Henry.Fry@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Iran;</t>
   </si>
   <si>
-    <t>Mathieson.Carlyle@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Norway;</t>
   </si>
   <si>
@@ -140,9 +125,6 @@
     <t>Haiti;New Zealand ;</t>
   </si>
   <si>
-    <t>Elliott.Bonnett@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Mexico;</t>
   </si>
   <si>
@@ -152,9 +134,6 @@
     <t>DR Congo;Panama;</t>
   </si>
   <si>
-    <t>Elliot.Davis@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Belgium;</t>
   </si>
   <si>
@@ -170,9 +149,6 @@
     <t>New Zealand ;Haiti;</t>
   </si>
   <si>
-    <t>Ann.Upchurch@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Brazil;</t>
   </si>
   <si>
@@ -182,9 +158,6 @@
     <t>Croatia;</t>
   </si>
   <si>
-    <t>Caleb.Matthews@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Ecuador;</t>
   </si>
   <si>
@@ -194,33 +167,21 @@
     <t>Uzbekistan;</t>
   </si>
   <si>
-    <t>Ollie.Martin@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Senegal;Ecuador;Croatia;</t>
   </si>
   <si>
     <t>Austria;Czech Republic;</t>
   </si>
   <si>
-    <t>Christo.Matheson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Iraq;</t>
   </si>
   <si>
-    <t>Daniel.Taylor@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Mexico;Japan;</t>
   </si>
   <si>
     <t>South Korea;Tunisia;</t>
   </si>
   <si>
-    <t>Frankie.Toland@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>England;Spain;France;</t>
   </si>
   <si>
@@ -248,60 +209,36 @@
     <t>New Zealand ;Qatar;Haiti;Curacao;Jordan;</t>
   </si>
   <si>
-    <t>Ryan.Wilkinson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>DR Congo;Uzbekistan;Iraq;Cape Verde;Panama;</t>
   </si>
   <si>
     <t>Jordan;Curacao;Haiti;Qatar;New Zealand ;</t>
   </si>
   <si>
-    <t>Max.Taylor-Smith@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Australia;South Africa;</t>
   </si>
   <si>
-    <t>Claudia.Wilkinson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Portugal;</t>
   </si>
   <si>
     <t>Algeria;</t>
   </si>
   <si>
-    <t>Kim.McCormick@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Croatia;Sweeden;</t>
   </si>
   <si>
     <t>Australia;Saudi Arabia;</t>
   </si>
   <si>
-    <t>Jackson.Middleton@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Cape Verde;</t>
   </si>
   <si>
-    <t>Abby.Robinson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Croatia;Switzerland;</t>
   </si>
   <si>
-    <t>Rose.Watson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Argentina;Portugal;</t>
   </si>
   <si>
-    <t>Karen.Rand@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>England;</t>
   </si>
   <si>
@@ -311,18 +248,12 @@
     <t>New Zealand ;</t>
   </si>
   <si>
-    <t>aidan.winder-speed@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Netherlands;Norway;</t>
   </si>
   <si>
     <t>New Zealand ;Jordan;</t>
   </si>
   <si>
-    <t>Matthew.Steiner@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Morocco;</t>
   </si>
   <si>
@@ -332,138 +263,48 @@
     <t>Scotland;Algeria;</t>
   </si>
   <si>
-    <t>Daniel.Pringle@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Paul.Cho@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Switzerland;</t>
   </si>
   <si>
-    <t>david.chrystall@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Switzerland;Sweeden;</t>
   </si>
   <si>
-    <t>Jordan.Hamilton@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Sam.Bull@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Ecuador;Senegal;Croatia;</t>
   </si>
   <si>
-    <t>Sartaj.Bedi@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Martha.Mallon@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>England;Spain;</t>
   </si>
   <si>
-    <t>Laura.Pringle@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>New Zealand ;Curacao;</t>
   </si>
   <si>
-    <t>Bridgette.Chisnall@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Luke.Archer@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Stephanie.McGregor@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Matthew.Bailey@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Switzerland;Croatia;</t>
   </si>
   <si>
-    <t>Matthew.Moloney@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Sven.Mol@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Tendai.Makova@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Bosnia;Paraguay;</t>
   </si>
   <si>
-    <t>Charlotte.Meyer@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>South Africa;</t>
   </si>
   <si>
-    <t>Charlotte.Brown@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Kylee.Garlick@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Rhyno.Heydenrych@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Marc.Lorentzen@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Austria;Egypt;</t>
   </si>
   <si>
-    <t>Kirsten.Dinnan@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Sylvie.Gray@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Michael.Chatwin2@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Abby.Galland@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>USA;</t>
   </si>
   <si>
-    <t>nick.wilkins@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Egypt;</t>
   </si>
   <si>
-    <t>Claire.Phipps@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Sarah.Bates2@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Croatia;Turkey;</t>
   </si>
   <si>
     <t>Tunisia;</t>
   </si>
   <si>
-    <t>Daniel.Wypych@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>South Korea;Iran;</t>
   </si>
   <si>
-    <t>Matthew.Lewer@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Jayden.Ravji@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Australia;Iran;South Korea;</t>
   </si>
   <si>
@@ -473,9 +314,6 @@
     <t>Qatar;Haiti;</t>
   </si>
   <si>
-    <t>Nicci.Coffey@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Colombia;</t>
   </si>
   <si>
@@ -485,130 +323,52 @@
     <t>Curacao;New Zealand ;</t>
   </si>
   <si>
-    <t>Irene.Kilford@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Spain;France;</t>
   </si>
   <si>
-    <t>Rachael.Peonides@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Natalie.Reid@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Zac.Clark@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Jenna.MachadodaCruz@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Ivory Coast;</t>
   </si>
   <si>
-    <t>Grant.McIntosh@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Harry.Trainor@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>France;Spain;</t>
   </si>
   <si>
-    <t>Simon.Wakefield@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Mexico;USA;</t>
   </si>
   <si>
     <t>Ecuador;Sweeden;</t>
   </si>
   <si>
-    <t>Olaf.Stypa@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Czech Republic;</t>
   </si>
   <si>
-    <t>Louise.Stephenson@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Scotland;Canada;</t>
   </si>
   <si>
-    <t>Paddy.Plunket@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Tunisia;Saudi Arabia;South Korea;Iran;South Africa;Australia;</t>
   </si>
   <si>
-    <t>Thulani.Mandiriza@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Matt.Croxford@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Ecuador;Croatia;</t>
   </si>
   <si>
     <t>Paraguay;</t>
   </si>
   <si>
-    <t>Finnan.Ralph@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Turkey;Switzerland;</t>
   </si>
   <si>
-    <t>Anna.Jefferson@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Robert.Chiu@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Japan;USA;</t>
   </si>
   <si>
     <t>South Korea;Australia;</t>
   </si>
   <si>
-    <t>Cameron.Megaw@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Ania.Mroczka@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Ricky.Ho@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Ecuador;Switzerland;</t>
   </si>
   <si>
-    <t>James.Evans@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Hamish.Buller@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Conor.Farrell@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Maree.VanderZouwe@comcom.govt.nz</t>
-  </si>
-  <si>
-    <t>Philia.Yeo@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>South Korea;Australia;Iran;</t>
   </si>
   <si>
-    <t>Elliot.Grant2@comcom.govt.nz</t>
-  </si>
-  <si>
     <t>Saudi Arabia;</t>
-  </si>
-  <si>
-    <t>anonymous</t>
   </si>
   <si>
     <t>Rosie Davies</t>
@@ -1118,26 +878,23 @@
       <c r="C2" s="1">
         <v>46176.619942129597</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
       <c r="F2" s="1">
         <v>46176.646435185197</v>
       </c>
       <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>18</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>19</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>20</v>
-      </c>
-      <c r="O2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -1150,20 +907,17 @@
       <c r="C3" s="1">
         <v>46176.634467592601</v>
       </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" s="1">
         <v>46176.636064814797</v>
       </c>
       <c r="G3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -1176,18 +930,15 @@
       <c r="C4" s="1">
         <v>46176.643888888902</v>
       </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" s="1"/>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -1200,18 +951,15 @@
       <c r="C5" s="1">
         <v>46176.644236111097</v>
       </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -1224,21 +972,18 @@
       <c r="C6" s="1">
         <v>46176.644282407397</v>
       </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="N6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -1251,21 +996,18 @@
       <c r="C7" s="1">
         <v>46176.645023148099</v>
       </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="N7" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1278,24 +1020,21 @@
       <c r="C8" s="1">
         <v>46176.645243055602</v>
       </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
       <c r="F8" s="1"/>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1308,21 +1047,18 @@
       <c r="C9" s="1">
         <v>46176.645370370403</v>
       </c>
-      <c r="D9" t="s">
-        <v>45</v>
-      </c>
       <c r="F9" s="1"/>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J9" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K9" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
@@ -1335,24 +1071,21 @@
       <c r="C10" s="1">
         <v>46176.645532407398</v>
       </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="N10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
@@ -1365,18 +1098,15 @@
       <c r="C11" s="1">
         <v>46176.645937499998</v>
       </c>
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" s="1"/>
       <c r="K11" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L11" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
@@ -1389,21 +1119,18 @@
       <c r="C12" s="1">
         <v>46176.645949074104</v>
       </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
       <c r="F12" s="1"/>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N12" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
@@ -1416,18 +1143,15 @@
       <c r="C13" s="1">
         <v>46176.646585648101</v>
       </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
       <c r="F13" s="1"/>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="K13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" t="s">
         <v>48</v>
-      </c>
-      <c r="M13" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -1440,36 +1164,33 @@
       <c r="C14" s="1">
         <v>46176.646932870397</v>
       </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I14" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="J14" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="K14" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L14" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="N14" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="O14" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
@@ -1482,18 +1203,15 @@
       <c r="C15" s="1">
         <v>46176.646944444401</v>
       </c>
-      <c r="D15" t="s">
-        <v>71</v>
-      </c>
       <c r="F15" s="1"/>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="N15" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="O15" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -1506,18 +1224,15 @@
       <c r="C16" s="1">
         <v>46176.6477662037</v>
       </c>
-      <c r="D16" t="s">
-        <v>74</v>
-      </c>
       <c r="F16" s="1"/>
       <c r="M16" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="N16" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -1530,18 +1245,15 @@
       <c r="C17" s="1">
         <v>46176.647847222201</v>
       </c>
-      <c r="D17" t="s">
-        <v>76</v>
-      </c>
       <c r="F17" s="1"/>
       <c r="H17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -1554,26 +1266,23 @@
       <c r="C18" s="1">
         <v>46176.648587962998</v>
       </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
       <c r="F18" s="1">
         <v>46184.3461805556</v>
       </c>
       <c r="J18" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K18" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="M18" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="N18" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -1586,21 +1295,18 @@
       <c r="C19" s="1">
         <v>46176.6488425926</v>
       </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
       <c r="F19" s="1"/>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="N19" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -1613,18 +1319,15 @@
       <c r="C20" s="1">
         <v>46176.6495601852</v>
       </c>
-      <c r="D20" t="s">
-        <v>84</v>
-      </c>
       <c r="F20" s="1"/>
       <c r="G20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="M20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -1637,15 +1340,12 @@
       <c r="C21" s="1">
         <v>46176.650023148097</v>
       </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
       <c r="F21" s="1"/>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -1658,18 +1358,15 @@
       <c r="C22" s="1">
         <v>46176.650266203702</v>
       </c>
-      <c r="D22" t="s">
-        <v>88</v>
-      </c>
       <c r="F22" s="1"/>
       <c r="G22" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="O22" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -1682,21 +1379,18 @@
       <c r="C23" s="1">
         <v>46176.650902777801</v>
       </c>
-      <c r="D23" t="s">
-        <v>92</v>
-      </c>
       <c r="F23" s="1"/>
       <c r="I23" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="M23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N23" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="O23" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -1709,21 +1403,18 @@
       <c r="C24" s="1">
         <v>46176.650902777801</v>
       </c>
-      <c r="D24" t="s">
-        <v>95</v>
-      </c>
       <c r="F24" s="1"/>
       <c r="J24" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="K24" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="L24" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="M24" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -1736,21 +1427,18 @@
       <c r="C25" s="1">
         <v>46176.651400463001</v>
       </c>
-      <c r="D25" t="s">
-        <v>99</v>
-      </c>
       <c r="F25" s="1"/>
       <c r="H25" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -1763,18 +1451,15 @@
       <c r="C26" s="1">
         <v>46176.653113425898</v>
       </c>
-      <c r="D26" t="s">
-        <v>100</v>
-      </c>
       <c r="F26" s="1"/>
       <c r="G26" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" t="s">
         <v>17</v>
       </c>
-      <c r="J26" t="s">
-        <v>18</v>
-      </c>
       <c r="K26" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -1787,18 +1472,15 @@
       <c r="C27" s="1">
         <v>46176.654432870397</v>
       </c>
-      <c r="D27" t="s">
-        <v>102</v>
-      </c>
       <c r="F27" s="1"/>
       <c r="G27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="M27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
@@ -1811,21 +1493,18 @@
       <c r="C28" s="1">
         <v>46176.655104166697</v>
       </c>
-      <c r="D28" t="s">
-        <v>104</v>
-      </c>
       <c r="F28" s="1"/>
       <c r="H28" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="O28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
@@ -1838,15 +1517,12 @@
       <c r="C29" s="1">
         <v>46176.662557870397</v>
       </c>
-      <c r="D29" t="s">
-        <v>105</v>
-      </c>
       <c r="F29" s="1"/>
       <c r="I29" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="K29" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -1859,24 +1535,21 @@
       <c r="C30" s="1">
         <v>46176.665879629603</v>
       </c>
-      <c r="D30" t="s">
-        <v>107</v>
-      </c>
       <c r="F30" s="1"/>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L30" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O30" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -1889,12 +1562,9 @@
       <c r="C31" s="1">
         <v>46176.668009259301</v>
       </c>
-      <c r="D31" t="s">
-        <v>108</v>
-      </c>
       <c r="F31" s="1"/>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -1907,21 +1577,18 @@
       <c r="C32" s="1">
         <v>46176.668472222198</v>
       </c>
-      <c r="D32" t="s">
-        <v>110</v>
-      </c>
       <c r="F32" s="1"/>
       <c r="H32" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="J32" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K32" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O32" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
@@ -1934,18 +1601,15 @@
       <c r="C33" s="1">
         <v>46176.6691319444</v>
       </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
       <c r="F33" s="1"/>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="K33" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
@@ -1958,21 +1622,18 @@
       <c r="C34" s="1">
         <v>46176.681388888901</v>
       </c>
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
       <c r="F34" s="1"/>
       <c r="H34" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J34" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K34" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O34" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
@@ -1985,18 +1646,15 @@
       <c r="C35" s="1">
         <v>46176.684641203698</v>
       </c>
-      <c r="D35" t="s">
-        <v>114</v>
-      </c>
       <c r="F35" s="1"/>
       <c r="G35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
@@ -2009,18 +1667,15 @@
       <c r="C36" s="1">
         <v>46176.6847569444</v>
       </c>
-      <c r="D36" t="s">
-        <v>115</v>
-      </c>
       <c r="F36" s="1"/>
       <c r="G36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K36" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="M36" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
@@ -2033,18 +1688,15 @@
       <c r="C37" s="1">
         <v>46176.7093171296</v>
       </c>
-      <c r="D37" t="s">
-        <v>117</v>
-      </c>
       <c r="F37" s="1"/>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
@@ -2057,18 +1709,15 @@
       <c r="C38" s="1">
         <v>46176.7570023148</v>
       </c>
-      <c r="D38" t="s">
-        <v>118</v>
-      </c>
       <c r="F38" s="1"/>
       <c r="G38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M38" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -2081,21 +1730,18 @@
       <c r="C39" s="1">
         <v>46177.010694444398</v>
       </c>
-      <c r="D39" t="s">
-        <v>119</v>
-      </c>
       <c r="F39" s="1"/>
       <c r="I39" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" t="s">
         <v>40</v>
       </c>
-      <c r="K39" t="s">
-        <v>48</v>
-      </c>
       <c r="L39" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="M39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
@@ -2108,18 +1754,15 @@
       <c r="C40" s="1">
         <v>46177.333530092597</v>
       </c>
-      <c r="D40" t="s">
-        <v>121</v>
-      </c>
       <c r="F40" s="1"/>
       <c r="G40" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="I40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M40" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
@@ -2132,12 +1775,9 @@
       <c r="C41" s="1">
         <v>46177.378946759301</v>
       </c>
-      <c r="D41" t="s">
-        <v>123</v>
-      </c>
       <c r="F41" s="1"/>
       <c r="G41" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
@@ -2150,24 +1790,21 @@
       <c r="C42" s="1">
         <v>46177.381782407399</v>
       </c>
-      <c r="D42" t="s">
-        <v>124</v>
-      </c>
       <c r="F42" s="1"/>
       <c r="G42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K42" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L42" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M42" t="s">
+        <v>31</v>
+      </c>
+      <c r="O42" t="s">
         <v>37</v>
-      </c>
-      <c r="O42" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
@@ -2180,21 +1817,18 @@
       <c r="C43" s="1">
         <v>46177.381990740701</v>
       </c>
-      <c r="D43" t="s">
-        <v>125</v>
-      </c>
       <c r="F43" s="1"/>
       <c r="H43" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J43" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L43" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="M43" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
@@ -2207,21 +1841,18 @@
       <c r="C44" s="1">
         <v>46177.384467592601</v>
       </c>
-      <c r="D44" t="s">
-        <v>126</v>
-      </c>
       <c r="F44" s="1"/>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K44" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L44" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="M44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
@@ -2234,18 +1865,15 @@
       <c r="C45" s="1">
         <v>46177.395682870403</v>
       </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
       <c r="F45" s="1"/>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="O45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
@@ -2258,18 +1886,15 @@
       <c r="C46" s="1">
         <v>46177.401261574101</v>
       </c>
-      <c r="D46" t="s">
-        <v>129</v>
-      </c>
       <c r="F46" s="1"/>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O46" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
@@ -2282,18 +1907,15 @@
       <c r="C47" s="1">
         <v>46177.406527777799</v>
       </c>
-      <c r="D47" t="s">
-        <v>130</v>
-      </c>
       <c r="F47" s="1"/>
       <c r="G47" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="J47" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K47" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
@@ -2306,18 +1928,15 @@
       <c r="C48" s="1">
         <v>46177.426354166702</v>
       </c>
-      <c r="D48" t="s">
-        <v>131</v>
-      </c>
       <c r="F48" s="1"/>
       <c r="G48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J48" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
@@ -2330,21 +1949,18 @@
       <c r="C49" s="1">
         <v>46177.480682870402</v>
       </c>
-      <c r="D49" t="s">
-        <v>133</v>
-      </c>
       <c r="F49" s="1"/>
       <c r="H49" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="K49" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L49" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
@@ -2357,18 +1973,15 @@
       <c r="C50" s="1">
         <v>46177.611122685201</v>
       </c>
-      <c r="D50" t="s">
-        <v>135</v>
-      </c>
       <c r="F50" s="1"/>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H50" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
@@ -2381,24 +1994,21 @@
       <c r="C51" s="1">
         <v>46177.677743055603</v>
       </c>
-      <c r="D51" t="s">
-        <v>136</v>
-      </c>
       <c r="F51" s="1"/>
       <c r="I51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K51" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="M51" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="N51" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="O51" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
@@ -2411,21 +2021,18 @@
       <c r="C52" s="1">
         <v>46177.7012384259</v>
       </c>
-      <c r="D52" t="s">
-        <v>139</v>
-      </c>
       <c r="F52" s="1"/>
       <c r="J52" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="K52" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L52" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="M52" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
@@ -2438,21 +2045,18 @@
       <c r="C53" s="1">
         <v>46177.711539351803</v>
       </c>
-      <c r="D53" t="s">
-        <v>141</v>
-      </c>
       <c r="F53" s="1"/>
       <c r="H53" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M53" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
@@ -2465,21 +2069,18 @@
       <c r="C54" s="1">
         <v>46177.711678240703</v>
       </c>
-      <c r="D54" t="s">
-        <v>142</v>
-      </c>
       <c r="F54" s="1"/>
       <c r="G54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M54" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="N54" t="s">
-        <v>144</v>
+        <v>91</v>
       </c>
       <c r="O54" t="s">
-        <v>145</v>
+        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
@@ -2492,24 +2093,21 @@
       <c r="C55" s="1">
         <v>46177.879837963003</v>
       </c>
-      <c r="D55" t="s">
-        <v>146</v>
-      </c>
       <c r="F55" s="1"/>
       <c r="I55" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="K55" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L55" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="N55" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="O55" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
@@ -2522,12 +2120,9 @@
       <c r="C56" s="1">
         <v>46178.247546296298</v>
       </c>
-      <c r="D56" t="s">
-        <v>150</v>
-      </c>
       <c r="F56" s="1"/>
       <c r="G56" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
@@ -2540,18 +2135,15 @@
       <c r="C57" s="1">
         <v>46178.3500347222</v>
       </c>
-      <c r="D57" t="s">
-        <v>152</v>
-      </c>
       <c r="F57" s="1"/>
       <c r="G57" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="I57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
@@ -2564,18 +2156,15 @@
       <c r="C58" s="1">
         <v>46178.3539467593</v>
       </c>
-      <c r="D58" t="s">
-        <v>153</v>
-      </c>
       <c r="F58" s="1"/>
       <c r="G58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H58" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="N58" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
@@ -2588,20 +2177,17 @@
       <c r="C59" s="1">
         <v>46178.3766666667</v>
       </c>
-      <c r="D59" t="s">
-        <v>154</v>
-      </c>
       <c r="F59" s="1">
         <v>46178.3821412037</v>
       </c>
       <c r="G59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
         <v>23</v>
       </c>
-      <c r="H59" t="s">
-        <v>26</v>
-      </c>
       <c r="O59" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
@@ -2614,21 +2200,18 @@
       <c r="C60" s="1">
         <v>46178.426701388897</v>
       </c>
-      <c r="D60" t="s">
-        <v>155</v>
-      </c>
       <c r="F60" s="1"/>
       <c r="G60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L60" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="O60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
@@ -2641,21 +2224,18 @@
       <c r="C61" s="1">
         <v>46178.4547916667</v>
       </c>
-      <c r="D61" t="s">
-        <v>157</v>
-      </c>
       <c r="F61" s="1"/>
       <c r="H61" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="J61" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K61" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="O61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
@@ -2668,12 +2248,9 @@
       <c r="C62" s="1">
         <v>46178.459837962997</v>
       </c>
-      <c r="D62" t="s">
-        <v>158</v>
-      </c>
       <c r="F62" s="1"/>
       <c r="G62" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
@@ -2686,15 +2263,12 @@
       <c r="C63" s="1">
         <v>46178.465358796297</v>
       </c>
-      <c r="D63" t="s">
-        <v>160</v>
-      </c>
       <c r="F63" s="1"/>
       <c r="J63" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="K63" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
@@ -2707,18 +2281,15 @@
       <c r="C64" s="1">
         <v>46178.553252314799</v>
       </c>
-      <c r="D64" t="s">
-        <v>163</v>
-      </c>
       <c r="F64" s="1"/>
       <c r="H64" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L64" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
@@ -2731,21 +2302,18 @@
       <c r="C65" s="1">
         <v>46181.392592592601</v>
       </c>
-      <c r="D65" t="s">
-        <v>165</v>
-      </c>
       <c r="F65" s="1"/>
       <c r="H65" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K65" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="L65" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="O65" t="s">
-        <v>149</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
@@ -2758,18 +2326,15 @@
       <c r="C66" s="1">
         <v>46181.393981481502</v>
       </c>
-      <c r="D66" t="s">
-        <v>167</v>
-      </c>
       <c r="F66" s="1"/>
       <c r="M66" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="N66" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="O66" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
@@ -2782,12 +2347,9 @@
       <c r="C67" s="1">
         <v>46181.398506944402</v>
       </c>
-      <c r="D67" t="s">
-        <v>169</v>
-      </c>
       <c r="F67" s="1"/>
       <c r="G67" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
@@ -2800,18 +2362,15 @@
       <c r="C68" s="1">
         <v>46181.433229166701</v>
       </c>
-      <c r="D68" t="s">
-        <v>170</v>
-      </c>
       <c r="F68" s="1"/>
       <c r="H68" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="K68" t="s">
-        <v>171</v>
+        <v>104</v>
       </c>
       <c r="L68" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
@@ -2824,18 +2383,15 @@
       <c r="C69" s="1">
         <v>46181.637094907397</v>
       </c>
-      <c r="D69" t="s">
-        <v>173</v>
-      </c>
       <c r="F69" s="1"/>
       <c r="H69" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="K69" t="s">
-        <v>174</v>
+        <v>106</v>
       </c>
       <c r="L69" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
@@ -2848,21 +2404,18 @@
       <c r="C70" s="1">
         <v>46182.609456018501</v>
       </c>
-      <c r="D70" t="s">
-        <v>175</v>
-      </c>
       <c r="F70" s="1"/>
       <c r="H70" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="J70" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="L70" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="M70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
@@ -2875,18 +2428,15 @@
       <c r="C71" s="1">
         <v>46182.626099537003</v>
       </c>
-      <c r="D71" t="s">
-        <v>176</v>
-      </c>
       <c r="F71" s="1"/>
       <c r="J71" t="s">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="K71" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="M71" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
@@ -2899,18 +2449,15 @@
       <c r="C72" s="1">
         <v>46182.649814814802</v>
       </c>
-      <c r="D72" t="s">
-        <v>179</v>
-      </c>
       <c r="F72" s="1"/>
       <c r="H72" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="K72" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="L72" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
@@ -2923,21 +2470,18 @@
       <c r="C73" s="1">
         <v>46183.398240740702</v>
       </c>
-      <c r="D73" t="s">
-        <v>180</v>
-      </c>
       <c r="F73" s="1"/>
       <c r="I73" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J73" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K73" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="M73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
@@ -2950,18 +2494,15 @@
       <c r="C74" s="1">
         <v>46183.4283796296</v>
       </c>
-      <c r="D74" t="s">
-        <v>181</v>
-      </c>
       <c r="F74" s="1"/>
       <c r="G74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K74" t="s">
-        <v>182</v>
+        <v>109</v>
       </c>
       <c r="M74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
@@ -2974,18 +2515,15 @@
       <c r="C75" s="1">
         <v>46183.616145833301</v>
       </c>
-      <c r="D75" t="s">
-        <v>183</v>
-      </c>
       <c r="F75" s="1"/>
       <c r="G75" t="s">
+        <v>16</v>
+      </c>
+      <c r="J75" t="s">
         <v>17</v>
       </c>
-      <c r="J75" t="s">
-        <v>18</v>
-      </c>
       <c r="K75" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
@@ -2998,24 +2536,21 @@
       <c r="C76" s="1">
         <v>46183.632256944402</v>
       </c>
-      <c r="D76" t="s">
-        <v>184</v>
-      </c>
       <c r="F76" s="1"/>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K76" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L76" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="M76" t="s">
+        <v>18</v>
+      </c>
+      <c r="N76" t="s">
         <v>19</v>
-      </c>
-      <c r="N76" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -3028,18 +2563,15 @@
       <c r="C77" s="1">
         <v>46183.705995370401</v>
       </c>
-      <c r="D77" t="s">
-        <v>185</v>
-      </c>
       <c r="F77" s="1"/>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="K77" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
@@ -3052,18 +2584,15 @@
       <c r="C78" s="1">
         <v>46184.321180555598</v>
       </c>
-      <c r="D78" t="s">
-        <v>186</v>
-      </c>
       <c r="F78" s="1"/>
       <c r="G78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M78" t="s">
-        <v>190</v>
+        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
@@ -3076,21 +2605,18 @@
       <c r="C79" s="1">
         <v>46184.375601851803</v>
       </c>
-      <c r="D79" t="s">
-        <v>187</v>
-      </c>
       <c r="F79" s="1"/>
       <c r="G79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L79" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M79" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="O79" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
@@ -3103,18 +2629,15 @@
       <c r="C80" s="1">
         <v>46184.403912037</v>
       </c>
-      <c r="D80" t="s">
-        <v>189</v>
-      </c>
       <c r="F80" s="1"/>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K80" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="M80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
@@ -3127,15 +2650,12 @@
       <c r="C81" s="1">
         <v>46177.615717592598</v>
       </c>
-      <c r="D81" t="s">
-        <v>191</v>
-      </c>
       <c r="E81" t="s">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
@@ -3148,21 +2668,18 @@
       <c r="C82" s="1">
         <v>46177.619768518503</v>
       </c>
-      <c r="D82" t="s">
-        <v>191</v>
-      </c>
       <c r="E82" t="s">
-        <v>196</v>
+        <v>116</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" t="s">
         <v>23</v>
       </c>
-      <c r="H82" t="s">
-        <v>26</v>
-      </c>
       <c r="O82" t="s">
-        <v>194</v>
+        <v>114</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
@@ -3175,30 +2692,27 @@
       <c r="C83" s="1">
         <v>46177.638206018499</v>
       </c>
-      <c r="D83" t="s">
-        <v>191</v>
-      </c>
       <c r="E83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F83" s="1"/>
       <c r="J83" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="K83" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="L83" t="s">
-        <v>195</v>
+        <v>115</v>
       </c>
       <c r="M83" t="s">
+        <v>18</v>
+      </c>
+      <c r="N83" t="s">
         <v>19</v>
       </c>
-      <c r="N83" t="s">
-        <v>20</v>
-      </c>
       <c r="O83" t="s">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
@@ -3211,24 +2725,21 @@
       <c r="C84" s="1">
         <v>46178.289583333302</v>
       </c>
-      <c r="D84" t="s">
-        <v>191</v>
-      </c>
       <c r="E84" t="s">
-        <v>197</v>
+        <v>117</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" t="s">
+        <v>16</v>
+      </c>
+      <c r="J84" t="s">
         <v>17</v>
       </c>
-      <c r="J84" t="s">
-        <v>18</v>
-      </c>
       <c r="L84" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="O84" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
@@ -3241,21 +2752,18 @@
       <c r="C85" s="1">
         <v>46185.352928240703</v>
       </c>
-      <c r="D85" t="s">
-        <v>191</v>
-      </c>
       <c r="E85" t="s">
-        <v>198</v>
+        <v>118</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H85" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="N85" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
+++ b/src/Football_World_Cup_2026_Pick_Em_1-79.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samwr\Code\personal projects\world_cup_dashboard\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FF119A7-3B45-41E2-B192-21AB442934B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D084D60A-38CA-4B55-82B9-33CD798B21F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,9 +80,6 @@
 </t>
   </si>
   <si>
-    <t>Sam Wright</t>
-  </si>
-  <si>
     <t>Spain;</t>
   </si>
   <si>
@@ -386,10 +383,13 @@
     <t>Ciara Moriarty</t>
   </si>
   <si>
-    <t>Damon Muollo</t>
-  </si>
-  <si>
     <t>Alex Davies</t>
+  </si>
+  <si>
+    <t>Saym Wright</t>
+  </si>
+  <si>
+    <t>Damo Muollo</t>
   </si>
 </sst>
 </file>
@@ -882,19 +882,19 @@
         <v>46176.646435185197</v>
       </c>
       <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="M2" t="s">
         <v>17</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>18</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -911,13 +911,13 @@
         <v>46176.636064814797</v>
       </c>
       <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -932,13 +932,13 @@
       </c>
       <c r="F4" s="1"/>
       <c r="H4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -953,13 +953,13 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
         <v>21</v>
       </c>
-      <c r="I5" t="s">
-        <v>22</v>
-      </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -974,16 +974,16 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" t="s">
         <v>27</v>
       </c>
-      <c r="N6" t="s">
+      <c r="O6" t="s">
         <v>28</v>
-      </c>
-      <c r="O6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -998,16 +998,16 @@
       </c>
       <c r="F7" s="1"/>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
         <v>30</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>31</v>
-      </c>
-      <c r="N7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1022,19 +1022,19 @@
       </c>
       <c r="F8" s="1"/>
       <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" t="s">
         <v>33</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>34</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>35</v>
       </c>
-      <c r="M8" t="s">
+      <c r="O8" t="s">
         <v>36</v>
-      </c>
-      <c r="O8" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1049,16 +1049,16 @@
       </c>
       <c r="F9" s="1"/>
       <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" t="s">
         <v>38</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K9" t="s">
         <v>39</v>
       </c>
-      <c r="K9" t="s">
-        <v>40</v>
-      </c>
       <c r="N9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
@@ -1073,19 +1073,19 @@
       </c>
       <c r="F10" s="1"/>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
         <v>41</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>42</v>
       </c>
-      <c r="N10" t="s">
-        <v>43</v>
-      </c>
       <c r="O10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
@@ -1100,13 +1100,13 @@
       </c>
       <c r="F11" s="1"/>
       <c r="K11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" t="s">
         <v>44</v>
       </c>
-      <c r="L11" t="s">
-        <v>45</v>
-      </c>
       <c r="M11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="F12" s="1"/>
       <c r="H12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
@@ -1145,13 +1145,13 @@
       </c>
       <c r="F13" s="1"/>
       <c r="J13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" t="s">
         <v>47</v>
-      </c>
-      <c r="K13" t="s">
-        <v>40</v>
-      </c>
-      <c r="M13" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -1166,31 +1166,31 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
         <v>49</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>50</v>
       </c>
-      <c r="I14" t="s">
+      <c r="J14" t="s">
         <v>51</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>52</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>53</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>54</v>
       </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>55</v>
       </c>
-      <c r="N14" t="s">
+      <c r="O14" t="s">
         <v>56</v>
-      </c>
-      <c r="O14" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
@@ -1205,13 +1205,13 @@
       </c>
       <c r="F15" s="1"/>
       <c r="M15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N15" t="s">
+        <v>57</v>
+      </c>
+      <c r="O15" t="s">
         <v>58</v>
-      </c>
-      <c r="O15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
@@ -1226,13 +1226,13 @@
       </c>
       <c r="F16" s="1"/>
       <c r="M16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="O16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -1247,13 +1247,13 @@
       </c>
       <c r="F17" s="1"/>
       <c r="H17" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="L17" t="s">
         <v>61</v>
-      </c>
-      <c r="I17" t="s">
-        <v>33</v>
-      </c>
-      <c r="L17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
@@ -1270,19 +1270,19 @@
         <v>46184.3461805556</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K18" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" t="s">
         <v>63</v>
       </c>
-      <c r="M18" t="s">
-        <v>64</v>
-      </c>
       <c r="N18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -1297,16 +1297,16 @@
       </c>
       <c r="F19" s="1"/>
       <c r="H19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -1321,13 +1321,13 @@
       </c>
       <c r="F20" s="1"/>
       <c r="G20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -1342,10 +1342,10 @@
       </c>
       <c r="F21" s="1"/>
       <c r="H21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -1360,13 +1360,13 @@
       </c>
       <c r="F22" s="1"/>
       <c r="G22" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" t="s">
         <v>68</v>
       </c>
-      <c r="H22" t="s">
+      <c r="O22" t="s">
         <v>69</v>
-      </c>
-      <c r="O22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -1381,16 +1381,16 @@
       </c>
       <c r="F23" s="1"/>
       <c r="I23" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" t="s">
         <v>71</v>
-      </c>
-      <c r="M23" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" t="s">
-        <v>43</v>
-      </c>
-      <c r="O23" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
@@ -1405,16 +1405,16 @@
       </c>
       <c r="F24" s="1"/>
       <c r="J24" t="s">
+        <v>72</v>
+      </c>
+      <c r="K24" t="s">
         <v>73</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>74</v>
       </c>
-      <c r="L24" t="s">
-        <v>75</v>
-      </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -1429,16 +1429,16 @@
       </c>
       <c r="F25" s="1"/>
       <c r="H25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -1453,13 +1453,13 @@
       </c>
       <c r="F26" s="1"/>
       <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="J26" t="s">
         <v>16</v>
       </c>
-      <c r="J26" t="s">
-        <v>17</v>
-      </c>
       <c r="K26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -1474,13 +1474,13 @@
       </c>
       <c r="F27" s="1"/>
       <c r="G27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M27" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
@@ -1495,16 +1495,16 @@
       </c>
       <c r="F28" s="1"/>
       <c r="H28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
@@ -1519,10 +1519,10 @@
       </c>
       <c r="F29" s="1"/>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -1537,19 +1537,19 @@
       </c>
       <c r="F30" s="1"/>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M30" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="F31" s="1"/>
       <c r="G31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -1579,16 +1579,16 @@
       </c>
       <c r="F32" s="1"/>
       <c r="H32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
@@ -1603,13 +1603,13 @@
       </c>
       <c r="F33" s="1"/>
       <c r="G33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
@@ -1624,16 +1624,16 @@
       </c>
       <c r="F34" s="1"/>
       <c r="H34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
@@ -1648,13 +1648,13 @@
       </c>
       <c r="F35" s="1"/>
       <c r="G35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
@@ -1669,13 +1669,13 @@
       </c>
       <c r="F36" s="1"/>
       <c r="G36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
@@ -1690,13 +1690,13 @@
       </c>
       <c r="F37" s="1"/>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
@@ -1711,13 +1711,13 @@
       </c>
       <c r="F38" s="1"/>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -1732,16 +1732,16 @@
       </c>
       <c r="F39" s="1"/>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L39" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M39" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
@@ -1756,13 +1756,13 @@
       </c>
       <c r="F40" s="1"/>
       <c r="G40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="F41" s="1"/>
       <c r="G41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
@@ -1792,19 +1792,19 @@
       </c>
       <c r="F42" s="1"/>
       <c r="G42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O42" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
@@ -1819,16 +1819,16 @@
       </c>
       <c r="F43" s="1"/>
       <c r="H43" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
@@ -1843,16 +1843,16 @@
       </c>
       <c r="F44" s="1"/>
       <c r="I44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L44" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
@@ -1867,13 +1867,13 @@
       </c>
       <c r="F45" s="1"/>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
@@ -1888,13 +1888,13 @@
       </c>
       <c r="F46" s="1"/>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O46" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
@@ -1909,13 +1909,13 @@
       </c>
       <c r="F47" s="1"/>
       <c r="G47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
@@ -1930,13 +1930,13 @@
       </c>
       <c r="F48" s="1"/>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
@@ -1951,16 +1951,16 @@
       </c>
       <c r="F49" s="1"/>
       <c r="H49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M49" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
@@ -1975,13 +1975,13 @@
       </c>
       <c r="F50" s="1"/>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
@@ -1996,19 +1996,19 @@
       </c>
       <c r="F51" s="1"/>
       <c r="I51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K51" t="s">
+        <v>86</v>
+      </c>
+      <c r="M51" t="s">
         <v>87</v>
       </c>
-      <c r="M51" t="s">
-        <v>88</v>
-      </c>
       <c r="N51" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O51" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
@@ -2023,16 +2023,16 @@
       </c>
       <c r="F52" s="1"/>
       <c r="J52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M52" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
@@ -2047,16 +2047,16 @@
       </c>
       <c r="F53" s="1"/>
       <c r="H53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
@@ -2071,16 +2071,16 @@
       </c>
       <c r="F54" s="1"/>
       <c r="G54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M54" t="s">
+        <v>89</v>
+      </c>
+      <c r="N54" t="s">
         <v>90</v>
       </c>
-      <c r="N54" t="s">
+      <c r="O54" t="s">
         <v>91</v>
-      </c>
-      <c r="O54" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
@@ -2095,19 +2095,19 @@
       </c>
       <c r="F55" s="1"/>
       <c r="I55" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" t="s">
+        <v>39</v>
+      </c>
+      <c r="L55" t="s">
         <v>93</v>
       </c>
-      <c r="K55" t="s">
-        <v>40</v>
-      </c>
-      <c r="L55" t="s">
+      <c r="N55" t="s">
+        <v>64</v>
+      </c>
+      <c r="O55" t="s">
         <v>94</v>
-      </c>
-      <c r="N55" t="s">
-        <v>65</v>
-      </c>
-      <c r="O55" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="F56" s="1"/>
       <c r="G56" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
@@ -2137,13 +2137,13 @@
       </c>
       <c r="F57" s="1"/>
       <c r="G57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I57" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M57" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
@@ -2158,13 +2158,13 @@
       </c>
       <c r="F58" s="1"/>
       <c r="G58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
@@ -2181,13 +2181,13 @@
         <v>46178.3821412037</v>
       </c>
       <c r="G59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
@@ -2202,16 +2202,16 @@
       </c>
       <c r="F60" s="1"/>
       <c r="G60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L60" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
@@ -2226,16 +2226,16 @@
       </c>
       <c r="F61" s="1"/>
       <c r="H61" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="F62" s="1"/>
       <c r="G62" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
@@ -2265,10 +2265,10 @@
       </c>
       <c r="F63" s="1"/>
       <c r="J63" t="s">
+        <v>98</v>
+      </c>
+      <c r="K63" t="s">
         <v>99</v>
-      </c>
-      <c r="K63" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
@@ -2283,13 +2283,13 @@
       </c>
       <c r="F64" s="1"/>
       <c r="H64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L64" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
@@ -2304,16 +2304,16 @@
       </c>
       <c r="F65" s="1"/>
       <c r="H65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
@@ -2328,13 +2328,13 @@
       </c>
       <c r="F66" s="1"/>
       <c r="M66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N66" t="s">
+        <v>55</v>
+      </c>
+      <c r="O66" t="s">
         <v>56</v>
-      </c>
-      <c r="O66" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="F67" s="1"/>
       <c r="G67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
@@ -2364,13 +2364,13 @@
       </c>
       <c r="F68" s="1"/>
       <c r="H68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K68" t="s">
+        <v>103</v>
+      </c>
+      <c r="L68" t="s">
         <v>104</v>
-      </c>
-      <c r="L68" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
@@ -2385,13 +2385,13 @@
       </c>
       <c r="F69" s="1"/>
       <c r="H69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K69" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
@@ -2406,16 +2406,16 @@
       </c>
       <c r="F70" s="1"/>
       <c r="H70" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
@@ -2430,13 +2430,13 @@
       </c>
       <c r="F71" s="1"/>
       <c r="J71" t="s">
+        <v>106</v>
+      </c>
+      <c r="K71" t="s">
+        <v>39</v>
+      </c>
+      <c r="M71" t="s">
         <v>107</v>
-      </c>
-      <c r="K71" t="s">
-        <v>40</v>
-      </c>
-      <c r="M71" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
@@ -2451,13 +2451,13 @@
       </c>
       <c r="F72" s="1"/>
       <c r="H72" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
@@ -2472,16 +2472,16 @@
       </c>
       <c r="F73" s="1"/>
       <c r="I73" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" t="s">
+        <v>38</v>
+      </c>
+      <c r="K73" t="s">
         <v>33</v>
       </c>
-      <c r="J73" t="s">
-        <v>39</v>
-      </c>
-      <c r="K73" t="s">
-        <v>34</v>
-      </c>
       <c r="M73" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
@@ -2496,13 +2496,13 @@
       </c>
       <c r="F74" s="1"/>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
@@ -2517,13 +2517,13 @@
       </c>
       <c r="F75" s="1"/>
       <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="J75" t="s">
         <v>16</v>
       </c>
-      <c r="J75" t="s">
-        <v>17</v>
-      </c>
       <c r="K75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
@@ -2538,19 +2538,19 @@
       </c>
       <c r="F76" s="1"/>
       <c r="G76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M76" t="s">
+        <v>17</v>
+      </c>
+      <c r="N76" t="s">
         <v>18</v>
-      </c>
-      <c r="N76" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
@@ -2565,13 +2565,13 @@
       </c>
       <c r="F77" s="1"/>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J77" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
@@ -2586,13 +2586,13 @@
       </c>
       <c r="F78" s="1"/>
       <c r="G78" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s">
         <v>21</v>
       </c>
-      <c r="I78" t="s">
-        <v>22</v>
-      </c>
       <c r="M78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
@@ -2607,16 +2607,16 @@
       </c>
       <c r="F79" s="1"/>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M79" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O79" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
@@ -2631,13 +2631,13 @@
       </c>
       <c r="F80" s="1"/>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M80" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.35">
@@ -2651,11 +2651,11 @@
         <v>46177.615717592598</v>
       </c>
       <c r="E81" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.35">
@@ -2669,17 +2669,17 @@
         <v>46177.619768518503</v>
       </c>
       <c r="E82" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O82" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.35">
@@ -2693,26 +2693,26 @@
         <v>46177.638206018499</v>
       </c>
       <c r="E83" t="s">
-        <v>15</v>
+        <v>117</v>
       </c>
       <c r="F83" s="1"/>
       <c r="J83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M83" t="s">
+        <v>17</v>
+      </c>
+      <c r="N83" t="s">
         <v>18</v>
       </c>
-      <c r="N83" t="s">
-        <v>19</v>
-      </c>
       <c r="O83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.35">
@@ -2726,20 +2726,20 @@
         <v>46178.289583333302</v>
       </c>
       <c r="E84" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F84" s="1"/>
       <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="J84" t="s">
         <v>16</v>
       </c>
-      <c r="J84" t="s">
-        <v>17</v>
-      </c>
       <c r="L84" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.35">
@@ -2753,17 +2753,17 @@
         <v>46185.352928240703</v>
       </c>
       <c r="E85" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F85" s="1"/>
       <c r="G85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H85" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
